--- a/ig/DM-AVRIL-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-TRE-G09-DepartementOM.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -883,25 +883,25 @@
     <t>91352</t>
   </si>
   <si>
-    <t>Département D'Alger et Orleansville (91352)</t>
+    <t>Alger</t>
   </si>
   <si>
     <t>92352</t>
   </si>
   <si>
-    <t>Département D'Oran et Bou Sfer (92352)</t>
+    <t>Oran</t>
   </si>
   <si>
     <t>93352</t>
   </si>
   <si>
-    <t>Département de Constantine (93352)</t>
+    <t>Constantine</t>
   </si>
   <si>
     <t>94352</t>
   </si>
   <si>
-    <t>Sud de l'Algérie (94352)</t>
+    <t>Territoires du sud de l'Algérie</t>
   </si>
   <si>
     <t>98000</t>
